--- a/projects/rdc-bms-room-allocation/Appendix_A_Asset_Register_RDC_BMS_rooms.xlsx
+++ b/projects/rdc-bms-room-allocation/Appendix_A_Asset_Register_RDC_BMS_rooms.xlsx
@@ -579,21 +579,21 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  295 of 1759 rows carry a reading; 1464 are still open.</t>
+          <t xml:space="preserve">  305 of 1759 rows carry a reading; 1454 are still open.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  90 SAME, 46 DIFF, 12 CONVENTION, 147 CHECK.</t>
+          <t xml:space="preserve">  90 SAME, 49 DIFF, 12 CONVENTION, 154 CHECK.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  205 rows are filled green across A:K - every DIFF, CONVENTION and CHECK.</t>
+          <t xml:space="preserve">  215 rows are filled green across A:K - every DIFF, CONVENTION and CHECK.</t>
         </is>
       </c>
     </row>
@@ -2462,70 +2462,96 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_GF_VAV4071A_VEV4074A</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>VAV</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Not Included</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Open High Bay Lab N-0215D</t>
         </is>
       </c>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Level 0 Open High Bay Lab N-0215D</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>read on the first floor screen; double-height space</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_GF_VAV4071B_VEV4074B</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>VAV</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Not Included</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Open High Bay Lab N-0215D</t>
         </is>
       </c>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Level 0 Open High Bay Lab N-0215D</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>read on the first floor screen; double-height space</t>
         </is>
       </c>
     </row>
@@ -21270,36 +21296,49 @@
       <c r="M542" s="2" t="inlineStr"/>
     </row>
     <row r="543">
-      <c r="A543" t="inlineStr">
+      <c r="A543" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_VAV4565_EV4566</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B543" s="5" t="inlineStr">
         <is>
           <t>EV</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>Included</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
         <is>
           <t>Conference N-1213</t>
         </is>
       </c>
-      <c r="J543" s="2" t="n"/>
-      <c r="K543" s="2" t="n"/>
+      <c r="E543" s="5" t="n"/>
+      <c r="F543" s="5" t="n"/>
+      <c r="G543" s="5" t="n"/>
+      <c r="H543" s="5" t="n"/>
+      <c r="I543" s="5" t="n"/>
+      <c r="J543" s="6" t="inlineStr">
+        <is>
+          <t>Storage Room N-1215</t>
+        </is>
+      </c>
+      <c r="K543" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L543" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DIFF</t>
         </is>
       </c>
       <c r="M543" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the screen puts NB-VAV4565-EV4566 in Storage Room N-1215; the register says Conference N-1213 - the dot sits on the room's left-hand wall</t>
         </is>
       </c>
     </row>
@@ -21414,36 +21453,49 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="inlineStr">
+      <c r="A547" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_VAV4600</t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B547" s="5" t="inlineStr">
         <is>
           <t>VAV</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr">
+      <c r="C547" s="5" t="inlineStr">
         <is>
           <t>Not Included</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr">
+      <c r="D547" s="5" t="inlineStr">
         <is>
           <t>Testing Room N-1216B</t>
         </is>
       </c>
-      <c r="J547" s="2" t="n"/>
-      <c r="K547" s="2" t="n"/>
+      <c r="E547" s="5" t="n"/>
+      <c r="F547" s="5" t="n"/>
+      <c r="G547" s="5" t="n"/>
+      <c r="H547" s="5" t="n"/>
+      <c r="I547" s="5" t="n"/>
+      <c r="J547" s="6" t="inlineStr">
+        <is>
+          <t>Testing Room N-1216B</t>
+        </is>
+      </c>
+      <c r="K547" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L547" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="M547" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the dot sits on the room's right-hand wall</t>
         </is>
       </c>
     </row>
@@ -21482,36 +21534,49 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
+      <c r="A549" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_VAV4620_VEV4621</t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B549" s="5" t="inlineStr">
         <is>
           <t>VEV</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C549" s="5" t="inlineStr">
         <is>
           <t>Not Included</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr">
+      <c r="D549" s="5" t="inlineStr">
         <is>
           <t>EL Shop N-1216C</t>
         </is>
       </c>
-      <c r="J549" s="2" t="n"/>
-      <c r="K549" s="2" t="n"/>
+      <c r="E549" s="5" t="n"/>
+      <c r="F549" s="5" t="n"/>
+      <c r="G549" s="5" t="n"/>
+      <c r="H549" s="5" t="n"/>
+      <c r="I549" s="5" t="n"/>
+      <c r="J549" s="6" t="inlineStr">
+        <is>
+          <t>EL Shop N-1216C</t>
+        </is>
+      </c>
+      <c r="K549" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L549" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="M549" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the dot sits on the room's right-hand wall</t>
         </is>
       </c>
     </row>
@@ -21996,104 +22061,143 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr">
+      <c r="A564" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_VAV4720</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B564" s="5" t="inlineStr">
         <is>
           <t>VAV</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>Included</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
+      <c r="C564" s="5" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+      <c r="D564" s="5" t="inlineStr">
         <is>
           <t>Office N-1239</t>
         </is>
       </c>
-      <c r="J564" s="2" t="n"/>
-      <c r="K564" s="2" t="n"/>
+      <c r="E564" s="5" t="n"/>
+      <c r="F564" s="5" t="n"/>
+      <c r="G564" s="5" t="n"/>
+      <c r="H564" s="5" t="n"/>
+      <c r="I564" s="5" t="n"/>
+      <c r="J564" s="6" t="inlineStr">
+        <is>
+          <t>Work Station N-1237</t>
+        </is>
+      </c>
+      <c r="K564" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L564" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DIFF</t>
         </is>
       </c>
       <c r="M564" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the screen puts NB-VAV4720 in Work Station N-1237; the register says Office N-1239 - the dot is in the open work station area right of Office N-1239</t>
         </is>
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr">
+      <c r="A565" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_VAV4725</t>
         </is>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B565" s="5" t="inlineStr">
         <is>
           <t>VAV</t>
         </is>
       </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>Included</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
         <is>
           <t>Office N-1240</t>
         </is>
       </c>
-      <c r="J565" s="2" t="n"/>
-      <c r="K565" s="2" t="n"/>
+      <c r="E565" s="5" t="n"/>
+      <c r="F565" s="5" t="n"/>
+      <c r="G565" s="5" t="n"/>
+      <c r="H565" s="5" t="n"/>
+      <c r="I565" s="5" t="n"/>
+      <c r="J565" s="6" t="inlineStr">
+        <is>
+          <t>Office N-1240</t>
+        </is>
+      </c>
+      <c r="K565" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L565" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="M565" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the dot sits on the room's right-hand wall</t>
         </is>
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr">
+      <c r="A566" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_VAV4730</t>
         </is>
       </c>
-      <c r="B566" t="inlineStr">
+      <c r="B566" s="5" t="inlineStr">
         <is>
           <t>VAV</t>
         </is>
       </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>Included</t>
-        </is>
-      </c>
-      <c r="D566" t="inlineStr">
+      <c r="C566" s="5" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+      <c r="D566" s="5" t="inlineStr">
         <is>
           <t>Office N-1241</t>
         </is>
       </c>
-      <c r="J566" s="2" t="n"/>
-      <c r="K566" s="2" t="n"/>
+      <c r="E566" s="5" t="n"/>
+      <c r="F566" s="5" t="n"/>
+      <c r="G566" s="5" t="n"/>
+      <c r="H566" s="5" t="n"/>
+      <c r="I566" s="5" t="n"/>
+      <c r="J566" s="6" t="inlineStr">
+        <is>
+          <t>Office N-1241</t>
+        </is>
+      </c>
+      <c r="K566" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L566" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="M566" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the dot sits on the room's right-hand wall</t>
         </is>
       </c>
     </row>
@@ -51514,36 +51618,49 @@
       </c>
     </row>
     <row r="1401">
-      <c r="A1401" t="inlineStr">
+      <c r="A1401" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_CEV-4502</t>
         </is>
       </c>
-      <c r="B1401" t="inlineStr">
+      <c r="B1401" s="5" t="inlineStr">
         <is>
           <t>CEV</t>
         </is>
       </c>
-      <c r="C1401" t="inlineStr">
-        <is>
-          <t>Included</t>
-        </is>
-      </c>
-      <c r="D1401" t="inlineStr">
+      <c r="C1401" s="5" t="inlineStr">
+        <is>
+          <t>Included</t>
+        </is>
+      </c>
+      <c r="D1401" s="5" t="inlineStr">
         <is>
           <t>Corridor N-1202</t>
         </is>
       </c>
-      <c r="J1401" s="2" t="n"/>
-      <c r="K1401" s="2" t="n"/>
+      <c r="E1401" s="5" t="n"/>
+      <c r="F1401" s="5" t="n"/>
+      <c r="G1401" s="5" t="n"/>
+      <c r="H1401" s="5" t="n"/>
+      <c r="I1401" s="5" t="n"/>
+      <c r="J1401" s="6" t="inlineStr">
+        <is>
+          <t>Level 0 Open High Bay Lab N-0215D</t>
+        </is>
+      </c>
+      <c r="K1401" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L1401" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DIFF</t>
         </is>
       </c>
       <c r="M1401" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the screen puts NB-CEV4502 in Level 0 Open High Bay Lab N-0215D; the register says Corridor N-1202 - the dot sits on the lab's lower wall; double-height space read on the first floor screen</t>
         </is>
       </c>
     </row>
@@ -51820,36 +51937,49 @@
       </c>
     </row>
     <row r="1410">
-      <c r="A1410" t="inlineStr">
+      <c r="A1410" s="5" t="inlineStr">
         <is>
           <t>RDC_NB_1F_FEV-4606</t>
         </is>
       </c>
-      <c r="B1410" t="inlineStr">
+      <c r="B1410" s="5" t="inlineStr">
         <is>
           <t>FEV</t>
         </is>
       </c>
-      <c r="C1410" t="inlineStr">
+      <c r="C1410" s="5" t="inlineStr">
         <is>
           <t>Not Included</t>
         </is>
       </c>
-      <c r="D1410" t="inlineStr">
+      <c r="D1410" s="5" t="inlineStr">
         <is>
           <t>Testing Room N-1216B</t>
         </is>
       </c>
-      <c r="J1410" s="2" t="n"/>
-      <c r="K1410" s="2" t="n"/>
+      <c r="E1410" s="5" t="n"/>
+      <c r="F1410" s="5" t="n"/>
+      <c r="G1410" s="5" t="n"/>
+      <c r="H1410" s="5" t="n"/>
+      <c r="I1410" s="5" t="n"/>
+      <c r="J1410" s="6" t="inlineStr">
+        <is>
+          <t>Testing Room N-1216B</t>
+        </is>
+      </c>
+      <c r="K1410" s="6" t="inlineStr">
+        <is>
+          <t>North Building/FF/FF-1</t>
+        </is>
+      </c>
       <c r="L1410" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="M1410" s="2" t="inlineStr">
         <is>
-          <t>no BMS screen reading for this unit</t>
+          <t>the dot sits on the wall between EL Shop N-1216C and Testing Room N-1216B, just inside Testing Room</t>
         </is>
       </c>
     </row>
